--- a/csv/model/DIC/formula_DIC_ON.xlsx
+++ b/csv/model/DIC/formula_DIC_ON.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <workbookPr/>
+  <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="33675" yWindow="3075" windowWidth="17280" windowHeight="8475" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="3624" yWindow="2148" windowWidth="17280" windowHeight="8880" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="191029" fullCalcOnLoad="1" iterate="1" calcCompleted="0" calcOnSave="0"/>
+  <calcPr calcId="191029" fullCalcOnLoad="1" calcOnSave="0"/>
 </workbook>
 </file>
 
@@ -440,7 +440,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
+  <sheetPr codeName="Sheet1">
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -592,7 +592,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>DIC_initial</t>
+          <t>dic_initial</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -677,7 +677,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>DIC_slope</t>
+          <t>dic_slope</t>
         </is>
       </c>
       <c r="M4" t="n">
@@ -757,7 +757,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>DIC_x50</t>
+          <t>dic_x50</t>
         </is>
       </c>
       <c r="M5" t="n">
@@ -837,7 +837,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>DIC_min</t>
+          <t>dic_min</t>
         </is>
       </c>
       <c r="M6" t="n">
@@ -917,7 +917,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>DIC_initial</t>
+          <t>dic_initial</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1002,7 +1002,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>DIC_slope</t>
+          <t>dic_slope</t>
         </is>
       </c>
       <c r="M8" t="n">
@@ -1082,7 +1082,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>DIC_x50</t>
+          <t>dic_x50</t>
         </is>
       </c>
       <c r="M9" t="n">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>DIC_min</t>
+          <t>dic_min</t>
         </is>
       </c>
       <c r="M10" t="n">
@@ -1242,7 +1242,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>DIC_initial</t>
+          <t>dic_initial</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1327,7 +1327,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>DIC_slope</t>
+          <t>dic_slope</t>
         </is>
       </c>
       <c r="M12" t="n">
@@ -1407,7 +1407,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>DIC_x50</t>
+          <t>dic_x50</t>
         </is>
       </c>
       <c r="M13" t="n">
@@ -1487,7 +1487,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>DIC_min</t>
+          <t>dic_min</t>
         </is>
       </c>
       <c r="M14" t="n">
@@ -1567,7 +1567,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>DIC_initial</t>
+          <t>dic_initial</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -1652,7 +1652,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>DIC_slope</t>
+          <t>dic_slope</t>
         </is>
       </c>
       <c r="M16" t="n">
@@ -1732,7 +1732,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>DIC_x50</t>
+          <t>dic_x50</t>
         </is>
       </c>
       <c r="M17" t="n">
@@ -1812,7 +1812,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>DIC_min</t>
+          <t>dic_min</t>
         </is>
       </c>
       <c r="M18" t="n">
@@ -1892,7 +1892,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>DIC_initial</t>
+          <t>dic_initial</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -1977,7 +1977,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>DIC_slope</t>
+          <t>dic_slope</t>
         </is>
       </c>
       <c r="M20" t="n">
@@ -2057,7 +2057,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>DIC_x50</t>
+          <t>dic_x50</t>
         </is>
       </c>
       <c r="M21" t="n">
@@ -2137,7 +2137,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>DIC_min</t>
+          <t>dic_min</t>
         </is>
       </c>
       <c r="M22" t="n">
@@ -2217,7 +2217,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>DIC_initial</t>
+          <t>dic_initial</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -2302,7 +2302,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>DIC_slope</t>
+          <t>dic_slope</t>
         </is>
       </c>
       <c r="M24" t="n">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>DIC_x50</t>
+          <t>dic_x50</t>
         </is>
       </c>
       <c r="M25" t="n">
@@ -2462,7 +2462,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>DIC_min</t>
+          <t>dic_min</t>
         </is>
       </c>
       <c r="M26" t="n">
@@ -2542,7 +2542,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>DIC_initial</t>
+          <t>dic_initial</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -2787,7 +2787,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>DIC_initial</t>
+          <t>dic_initial</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -3032,7 +3032,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>DIC_initial</t>
+          <t>dic_initial</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -3277,7 +3277,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>DIC_initial</t>
+          <t>dic_initial</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
@@ -3522,7 +3522,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>DIC_initial</t>
+          <t>dic_initial</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
@@ -3767,7 +3767,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>DIC_initial</t>
+          <t>dic_initial</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
@@ -4012,7 +4012,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>DIC_initial</t>
+          <t>dic_initial</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
@@ -4097,7 +4097,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>DIC_slope</t>
+          <t>dic_slope</t>
         </is>
       </c>
       <c r="M46" t="n">
@@ -4177,7 +4177,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>DIC_x50</t>
+          <t>dic_x50</t>
         </is>
       </c>
       <c r="M47" t="n">
@@ -4257,7 +4257,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>DIC_min</t>
+          <t>dic_min</t>
         </is>
       </c>
       <c r="M48" t="n">
@@ -4337,7 +4337,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>DIC_initial</t>
+          <t>dic_initial</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
@@ -4422,7 +4422,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>DIC_slope</t>
+          <t>dic_slope</t>
         </is>
       </c>
       <c r="M50" t="n">
@@ -4502,7 +4502,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>DIC_x50</t>
+          <t>dic_x50</t>
         </is>
       </c>
       <c r="M51" t="n">
@@ -4582,7 +4582,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>DIC_min</t>
+          <t>dic_min</t>
         </is>
       </c>
       <c r="M52" t="n">
@@ -4662,7 +4662,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>DIC_initial</t>
+          <t>dic_initial</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
@@ -4747,7 +4747,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>DIC_slope</t>
+          <t>dic_slope</t>
         </is>
       </c>
       <c r="M54" t="n">
@@ -4827,7 +4827,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>DIC_x50</t>
+          <t>dic_x50</t>
         </is>
       </c>
       <c r="M55" t="n">
@@ -4907,7 +4907,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>DIC_min</t>
+          <t>dic_min</t>
         </is>
       </c>
       <c r="M56" t="n">
@@ -4987,7 +4987,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>DIC_initial</t>
+          <t>dic_initial</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
@@ -5072,7 +5072,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>DIC_slope</t>
+          <t>dic_slope</t>
         </is>
       </c>
       <c r="M58" t="n">
@@ -5152,7 +5152,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>DIC_x50</t>
+          <t>dic_x50</t>
         </is>
       </c>
       <c r="M59" t="n">
@@ -5232,7 +5232,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>DIC_min</t>
+          <t>dic_min</t>
         </is>
       </c>
       <c r="M60" t="n">
@@ -5312,7 +5312,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>DIC_initial</t>
+          <t>dic_initial</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
@@ -5397,7 +5397,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>DIC_slope</t>
+          <t>dic_slope</t>
         </is>
       </c>
       <c r="M62" t="n">
@@ -5477,7 +5477,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>DIC_x50</t>
+          <t>dic_x50</t>
         </is>
       </c>
       <c r="M63" t="n">
@@ -5557,7 +5557,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>DIC_min</t>
+          <t>dic_min</t>
         </is>
       </c>
       <c r="M64" t="n">
@@ -5637,7 +5637,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>DIC_initial</t>
+          <t>dic_initial</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
@@ -5722,7 +5722,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>DIC_slope</t>
+          <t>dic_slope</t>
         </is>
       </c>
       <c r="M66" t="n">
@@ -5802,7 +5802,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>DIC_x50</t>
+          <t>dic_x50</t>
         </is>
       </c>
       <c r="M67" t="n">
@@ -5882,7 +5882,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>DIC_min</t>
+          <t>dic_min</t>
         </is>
       </c>
       <c r="M68" t="n">
@@ -5962,7 +5962,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>DIC_initial</t>
+          <t>dic_initial</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
@@ -6047,7 +6047,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>DIC_slope</t>
+          <t>dic_slope</t>
         </is>
       </c>
       <c r="M70" t="n">
@@ -6127,7 +6127,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>DIC_x50</t>
+          <t>dic_x50</t>
         </is>
       </c>
       <c r="M71" t="n">
@@ -6207,7 +6207,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>DIC_min</t>
+          <t>dic_min</t>
         </is>
       </c>
       <c r="M72" t="n">
@@ -6287,7 +6287,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>DIC_initial</t>
+          <t>dic_initial</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
@@ -6372,7 +6372,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>DIC_slope</t>
+          <t>dic_slope</t>
         </is>
       </c>
       <c r="M74" t="n">
@@ -6452,7 +6452,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>DIC_x50</t>
+          <t>dic_x50</t>
         </is>
       </c>
       <c r="M75" t="n">
@@ -6532,7 +6532,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>DIC_min</t>
+          <t>dic_min</t>
         </is>
       </c>
       <c r="M76" t="n">
@@ -6612,7 +6612,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>DIC_initial</t>
+          <t>dic_initial</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
@@ -6697,7 +6697,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>DIC_slope</t>
+          <t>dic_slope</t>
         </is>
       </c>
       <c r="M78" t="n">
@@ -6777,7 +6777,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>DIC_x50</t>
+          <t>dic_x50</t>
         </is>
       </c>
       <c r="M79" t="n">
@@ -6857,7 +6857,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>DIC_min</t>
+          <t>dic_min</t>
         </is>
       </c>
       <c r="M80" t="n">
@@ -6937,7 +6937,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>DIC_initial</t>
+          <t>dic_initial</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
@@ -7022,7 +7022,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>DIC_slope</t>
+          <t>dic_slope</t>
         </is>
       </c>
       <c r="M82" t="n">
@@ -7102,7 +7102,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>DIC_x50</t>
+          <t>dic_x50</t>
         </is>
       </c>
       <c r="M83" t="n">
@@ -7182,7 +7182,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>DIC_min</t>
+          <t>dic_min</t>
         </is>
       </c>
       <c r="M84" t="n">
@@ -7262,7 +7262,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>DIC_initial</t>
+          <t>dic_initial</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
@@ -7347,7 +7347,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>DIC_slope</t>
+          <t>dic_slope</t>
         </is>
       </c>
       <c r="M86" t="n">
@@ -7427,7 +7427,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>DIC_x50</t>
+          <t>dic_x50</t>
         </is>
       </c>
       <c r="M87" t="n">
@@ -7507,7 +7507,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>DIC_min</t>
+          <t>dic_min</t>
         </is>
       </c>
       <c r="M88" t="n">
@@ -7587,7 +7587,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>DIC_initial</t>
+          <t>dic_initial</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
@@ -7672,7 +7672,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>DIC_slope</t>
+          <t>dic_slope</t>
         </is>
       </c>
       <c r="M90" t="n">
@@ -7752,7 +7752,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>DIC_x50</t>
+          <t>dic_x50</t>
         </is>
       </c>
       <c r="M91" t="n">
@@ -7832,7 +7832,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>DIC_min</t>
+          <t>dic_min</t>
         </is>
       </c>
       <c r="M92" t="n">
@@ -7912,7 +7912,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>DIC_initial</t>
+          <t>dic_initial</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
@@ -7997,7 +7997,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>DIC_slope</t>
+          <t>dic_slope</t>
         </is>
       </c>
       <c r="M94" t="n">
@@ -8077,7 +8077,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>DIC_x50</t>
+          <t>dic_x50</t>
         </is>
       </c>
       <c r="M95" t="n">
@@ -8157,7 +8157,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>DIC_min</t>
+          <t>dic_min</t>
         </is>
       </c>
       <c r="M96" t="n">
@@ -8237,7 +8237,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>DIC_initial</t>
+          <t>dic_initial</t>
         </is>
       </c>
       <c r="L97" t="inlineStr">
@@ -8322,7 +8322,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>DIC_slope</t>
+          <t>dic_slope</t>
         </is>
       </c>
       <c r="M98" t="n">
@@ -8402,7 +8402,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>DIC_x50</t>
+          <t>dic_x50</t>
         </is>
       </c>
       <c r="M99" t="n">
@@ -8482,7 +8482,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>DIC_min</t>
+          <t>dic_min</t>
         </is>
       </c>
       <c r="M100" t="n">
@@ -8562,7 +8562,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>DIC_initial</t>
+          <t>dic_initial</t>
         </is>
       </c>
       <c r="L101" t="inlineStr">
@@ -8647,7 +8647,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>DIC_slope</t>
+          <t>dic_slope</t>
         </is>
       </c>
       <c r="M102" t="n">
@@ -8727,7 +8727,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>DIC_x50</t>
+          <t>dic_x50</t>
         </is>
       </c>
       <c r="M103" t="n">
@@ -8807,7 +8807,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>DIC_min</t>
+          <t>dic_min</t>
         </is>
       </c>
       <c r="M104" t="n">
@@ -8887,7 +8887,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>DIC_initial</t>
+          <t>dic_initial</t>
         </is>
       </c>
       <c r="L105" t="inlineStr">
@@ -8972,7 +8972,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>DIC_slope</t>
+          <t>dic_slope</t>
         </is>
       </c>
       <c r="M106" t="n">
@@ -9052,7 +9052,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>DIC_x50</t>
+          <t>dic_x50</t>
         </is>
       </c>
       <c r="M107" t="n">
@@ -9132,7 +9132,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>DIC_min</t>
+          <t>dic_min</t>
         </is>
       </c>
       <c r="M108" t="n">
@@ -9212,7 +9212,7 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>DIC_initial</t>
+          <t>dic_initial</t>
         </is>
       </c>
       <c r="L109" t="inlineStr">
@@ -9297,7 +9297,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>DIC_slope</t>
+          <t>dic_slope</t>
         </is>
       </c>
       <c r="M110" t="n">
@@ -9377,7 +9377,7 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>DIC_x50</t>
+          <t>dic_x50</t>
         </is>
       </c>
       <c r="M111" t="n">
@@ -9457,7 +9457,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>DIC_min</t>
+          <t>dic_min</t>
         </is>
       </c>
       <c r="M112" t="n">
@@ -9537,7 +9537,7 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>DIC_initial</t>
+          <t>dic_initial</t>
         </is>
       </c>
       <c r="L113" t="inlineStr">
@@ -9622,7 +9622,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>DIC_slope</t>
+          <t>dic_slope</t>
         </is>
       </c>
       <c r="M114" t="n">
@@ -9702,7 +9702,7 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>DIC_x50</t>
+          <t>dic_x50</t>
         </is>
       </c>
       <c r="M115" t="n">
@@ -9782,7 +9782,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>DIC_min</t>
+          <t>dic_min</t>
         </is>
       </c>
       <c r="M116" t="n">
@@ -9862,7 +9862,7 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>DIC_initial</t>
+          <t>dic_initial</t>
         </is>
       </c>
       <c r="L117" t="inlineStr">
@@ -9947,7 +9947,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>DIC_slope</t>
+          <t>dic_slope</t>
         </is>
       </c>
       <c r="M118" t="n">
@@ -10027,7 +10027,7 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>DIC_x50</t>
+          <t>dic_x50</t>
         </is>
       </c>
       <c r="M119" t="n">
@@ -10107,7 +10107,7 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>DIC_min</t>
+          <t>dic_min</t>
         </is>
       </c>
       <c r="M120" t="n">
@@ -10187,7 +10187,7 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>DIC_initial</t>
+          <t>dic_initial</t>
         </is>
       </c>
       <c r="L121" t="inlineStr">
@@ -10272,7 +10272,7 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>DIC_slope</t>
+          <t>dic_slope</t>
         </is>
       </c>
       <c r="M122" t="n">
@@ -10352,7 +10352,7 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>DIC_x50</t>
+          <t>dic_x50</t>
         </is>
       </c>
       <c r="M123" t="n">
@@ -10432,7 +10432,7 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>DIC_min</t>
+          <t>dic_min</t>
         </is>
       </c>
       <c r="M124" t="n">
@@ -10512,7 +10512,7 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>DIC_initial</t>
+          <t>dic_initial</t>
         </is>
       </c>
       <c r="L125" t="inlineStr">
@@ -10597,7 +10597,7 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>DIC_slope</t>
+          <t>dic_slope</t>
         </is>
       </c>
       <c r="M126" t="n">
@@ -10677,7 +10677,7 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>DIC_x50</t>
+          <t>dic_x50</t>
         </is>
       </c>
       <c r="M127" t="n">
@@ -10757,7 +10757,7 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>DIC_min</t>
+          <t>dic_min</t>
         </is>
       </c>
       <c r="M128" t="n">
@@ -10837,7 +10837,7 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>DIC_initial</t>
+          <t>dic_initial</t>
         </is>
       </c>
       <c r="L129" t="inlineStr">
@@ -10922,7 +10922,7 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>DIC_slope</t>
+          <t>dic_slope</t>
         </is>
       </c>
       <c r="M130" t="n">
@@ -11002,7 +11002,7 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>DIC_x50</t>
+          <t>dic_x50</t>
         </is>
       </c>
       <c r="M131" t="n">
@@ -11082,7 +11082,7 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>DIC_min</t>
+          <t>dic_min</t>
         </is>
       </c>
       <c r="M132" t="n">
@@ -11162,7 +11162,7 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>DIC_initial</t>
+          <t>dic_initial</t>
         </is>
       </c>
       <c r="L133" t="inlineStr">
@@ -11247,7 +11247,7 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>DIC_slope</t>
+          <t>dic_slope</t>
         </is>
       </c>
       <c r="M134" t="n">
@@ -11327,7 +11327,7 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>DIC_x50</t>
+          <t>dic_x50</t>
         </is>
       </c>
       <c r="M135" t="n">
@@ -11407,7 +11407,7 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>DIC_min</t>
+          <t>dic_min</t>
         </is>
       </c>
       <c r="M136" t="n">
@@ -11487,7 +11487,7 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>DIC_initial</t>
+          <t>dic_initial</t>
         </is>
       </c>
       <c r="L137" t="inlineStr">
@@ -11572,7 +11572,7 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>DIC_slope</t>
+          <t>dic_slope</t>
         </is>
       </c>
       <c r="M138" t="n">
@@ -11652,7 +11652,7 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>DIC_x50</t>
+          <t>dic_x50</t>
         </is>
       </c>
       <c r="M139" t="n">
@@ -11732,7 +11732,7 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>DIC_min</t>
+          <t>dic_min</t>
         </is>
       </c>
       <c r="M140" t="n">
@@ -11812,7 +11812,7 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>DIC_initial</t>
+          <t>dic_initial</t>
         </is>
       </c>
       <c r="L141" t="inlineStr">
@@ -11897,7 +11897,7 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>DIC_slope</t>
+          <t>dic_slope</t>
         </is>
       </c>
       <c r="M142" t="n">
@@ -11977,7 +11977,7 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>DIC_x50</t>
+          <t>dic_x50</t>
         </is>
       </c>
       <c r="M143" t="n">
@@ -12057,7 +12057,7 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>DIC_min</t>
+          <t>dic_min</t>
         </is>
       </c>
       <c r="M144" t="n">
@@ -12137,7 +12137,7 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>DIC_initial</t>
+          <t>dic_initial</t>
         </is>
       </c>
       <c r="L145" t="inlineStr">
@@ -12222,7 +12222,7 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>DIC_slope</t>
+          <t>dic_slope</t>
         </is>
       </c>
       <c r="M146" t="n">
@@ -12302,7 +12302,7 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>DIC_x50</t>
+          <t>dic_x50</t>
         </is>
       </c>
       <c r="M147" t="n">
@@ -12382,7 +12382,7 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>DIC_min</t>
+          <t>dic_min</t>
         </is>
       </c>
       <c r="M148" t="n">
@@ -12462,7 +12462,7 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>DIC_initial</t>
+          <t>dic_initial</t>
         </is>
       </c>
       <c r="L149" t="inlineStr">
@@ -12547,7 +12547,7 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>DIC_slope</t>
+          <t>dic_slope</t>
         </is>
       </c>
       <c r="M150" t="n">
@@ -12627,7 +12627,7 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>DIC_x50</t>
+          <t>dic_x50</t>
         </is>
       </c>
       <c r="M151" t="n">
@@ -12707,7 +12707,7 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>DIC_min</t>
+          <t>dic_min</t>
         </is>
       </c>
       <c r="M152" t="n">
@@ -12787,7 +12787,7 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>DIC_initial</t>
+          <t>dic_initial</t>
         </is>
       </c>
       <c r="L153" t="inlineStr">
@@ -12872,7 +12872,7 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>DIC_slope</t>
+          <t>dic_slope</t>
         </is>
       </c>
       <c r="M154" t="n">
@@ -12952,7 +12952,7 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>DIC_x50</t>
+          <t>dic_x50</t>
         </is>
       </c>
       <c r="M155" t="n">
@@ -13032,7 +13032,7 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>DIC_min</t>
+          <t>dic_min</t>
         </is>
       </c>
       <c r="M156" t="n">
@@ -13112,7 +13112,7 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>DIC_initial</t>
+          <t>dic_initial</t>
         </is>
       </c>
       <c r="L157" t="inlineStr">
@@ -13197,7 +13197,7 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>DIC_slope</t>
+          <t>dic_slope</t>
         </is>
       </c>
       <c r="M158" t="n">
@@ -13277,7 +13277,7 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>DIC_x50</t>
+          <t>dic_x50</t>
         </is>
       </c>
       <c r="M159" t="n">
@@ -13357,7 +13357,7 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>DIC_min</t>
+          <t>dic_min</t>
         </is>
       </c>
       <c r="M160" t="n">
@@ -13437,7 +13437,7 @@
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>DIC_initial</t>
+          <t>dic_initial</t>
         </is>
       </c>
       <c r="L161" t="inlineStr">
@@ -13522,7 +13522,7 @@
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>DIC_slope</t>
+          <t>dic_slope</t>
         </is>
       </c>
       <c r="M162" t="n">
@@ -13602,7 +13602,7 @@
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>DIC_x50</t>
+          <t>dic_x50</t>
         </is>
       </c>
       <c r="M163" t="n">
@@ -13682,7 +13682,7 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>DIC_min</t>
+          <t>dic_min</t>
         </is>
       </c>
       <c r="M164" t="n">
@@ -13762,7 +13762,7 @@
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>DIC_initial</t>
+          <t>dic_initial</t>
         </is>
       </c>
       <c r="L165" t="inlineStr">
@@ -13847,7 +13847,7 @@
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>DIC_slope</t>
+          <t>dic_slope</t>
         </is>
       </c>
       <c r="M166" t="n">
@@ -13927,7 +13927,7 @@
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>DIC_x50</t>
+          <t>dic_x50</t>
         </is>
       </c>
       <c r="M167" t="n">
@@ -14007,7 +14007,7 @@
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>DIC_min</t>
+          <t>dic_min</t>
         </is>
       </c>
       <c r="M168" t="n">
@@ -14087,7 +14087,7 @@
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>DIC_initial</t>
+          <t>dic_initial</t>
         </is>
       </c>
       <c r="L169" t="inlineStr">
@@ -14172,7 +14172,7 @@
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>DIC_slope</t>
+          <t>dic_slope</t>
         </is>
       </c>
       <c r="M170" t="n">
@@ -14252,7 +14252,7 @@
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>DIC_x50</t>
+          <t>dic_x50</t>
         </is>
       </c>
       <c r="M171" t="n">
@@ -14332,7 +14332,7 @@
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>DIC_min</t>
+          <t>dic_min</t>
         </is>
       </c>
       <c r="M172" t="n">
@@ -14412,7 +14412,7 @@
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>DIC_initial</t>
+          <t>dic_initial</t>
         </is>
       </c>
       <c r="L173" t="inlineStr">
@@ -14497,7 +14497,7 @@
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>DIC_slope</t>
+          <t>dic_slope</t>
         </is>
       </c>
       <c r="M174" t="n">
@@ -14577,7 +14577,7 @@
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>DIC_x50</t>
+          <t>dic_x50</t>
         </is>
       </c>
       <c r="M175" t="n">
@@ -14657,7 +14657,7 @@
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>DIC_min</t>
+          <t>dic_min</t>
         </is>
       </c>
       <c r="M176" t="n">
@@ -14737,7 +14737,7 @@
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>DIC_initial</t>
+          <t>dic_initial</t>
         </is>
       </c>
       <c r="L177" t="inlineStr">
@@ -14822,7 +14822,7 @@
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>DIC_slope</t>
+          <t>dic_slope</t>
         </is>
       </c>
       <c r="M178" t="n">
@@ -14902,7 +14902,7 @@
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>DIC_x50</t>
+          <t>dic_x50</t>
         </is>
       </c>
       <c r="M179" t="n">
@@ -14982,7 +14982,7 @@
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>DIC_min</t>
+          <t>dic_min</t>
         </is>
       </c>
       <c r="M180" t="n">
@@ -15062,7 +15062,7 @@
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>DIC_initial</t>
+          <t>dic_initial</t>
         </is>
       </c>
       <c r="L181" t="inlineStr">
@@ -15147,7 +15147,7 @@
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>DIC_slope</t>
+          <t>dic_slope</t>
         </is>
       </c>
       <c r="M182" t="n">
@@ -15227,7 +15227,7 @@
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>DIC_x50</t>
+          <t>dic_x50</t>
         </is>
       </c>
       <c r="M183" t="n">
@@ -15307,7 +15307,7 @@
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>DIC_min</t>
+          <t>dic_min</t>
         </is>
       </c>
       <c r="M184" t="n">
@@ -15387,7 +15387,7 @@
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>DIC_initial</t>
+          <t>dic_initial</t>
         </is>
       </c>
       <c r="L185" t="inlineStr">
@@ -15472,7 +15472,7 @@
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>DIC_slope</t>
+          <t>dic_slope</t>
         </is>
       </c>
       <c r="M186" t="n">
@@ -15552,7 +15552,7 @@
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>DIC_x50</t>
+          <t>dic_x50</t>
         </is>
       </c>
       <c r="M187" t="n">
@@ -15632,7 +15632,7 @@
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>DIC_min</t>
+          <t>dic_min</t>
         </is>
       </c>
       <c r="M188" t="n">
@@ -15712,7 +15712,7 @@
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>DIC_initial</t>
+          <t>dic_initial</t>
         </is>
       </c>
       <c r="L189" t="inlineStr">
@@ -15797,7 +15797,7 @@
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>DIC_slope</t>
+          <t>dic_slope</t>
         </is>
       </c>
       <c r="M190" t="n">
@@ -15877,7 +15877,7 @@
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>DIC_x50</t>
+          <t>dic_x50</t>
         </is>
       </c>
       <c r="M191" t="n">
@@ -15957,7 +15957,7 @@
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>DIC_min</t>
+          <t>dic_min</t>
         </is>
       </c>
       <c r="M192" t="n">
@@ -16037,7 +16037,7 @@
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>DIC_initial</t>
+          <t>dic_initial</t>
         </is>
       </c>
       <c r="L193" t="inlineStr">
@@ -16122,7 +16122,7 @@
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>DIC_slope</t>
+          <t>dic_slope</t>
         </is>
       </c>
       <c r="M194" t="n">
@@ -16202,7 +16202,7 @@
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>DIC_x50</t>
+          <t>dic_x50</t>
         </is>
       </c>
       <c r="M195" t="n">
@@ -16282,7 +16282,7 @@
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>DIC_min</t>
+          <t>dic_min</t>
         </is>
       </c>
       <c r="M196" t="n">
@@ -16362,7 +16362,7 @@
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>DIC_initial</t>
+          <t>dic_initial</t>
         </is>
       </c>
       <c r="L197" t="inlineStr">
@@ -16447,7 +16447,7 @@
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>DIC_slope</t>
+          <t>dic_slope</t>
         </is>
       </c>
       <c r="M198" t="n">
@@ -16527,7 +16527,7 @@
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>DIC_x50</t>
+          <t>dic_x50</t>
         </is>
       </c>
       <c r="M199" t="n">
@@ -16607,7 +16607,7 @@
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>DIC_min</t>
+          <t>dic_min</t>
         </is>
       </c>
       <c r="M200" t="n">
@@ -16687,7 +16687,7 @@
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>DIC_initial</t>
+          <t>dic_initial</t>
         </is>
       </c>
       <c r="L201" t="inlineStr">
@@ -16772,7 +16772,7 @@
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>DIC_slope</t>
+          <t>dic_slope</t>
         </is>
       </c>
       <c r="M202" t="n">
@@ -16852,7 +16852,7 @@
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>DIC_x50</t>
+          <t>dic_x50</t>
         </is>
       </c>
       <c r="M203" t="n">
@@ -16932,7 +16932,7 @@
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>DIC_min</t>
+          <t>dic_min</t>
         </is>
       </c>
       <c r="M204" t="n">
@@ -17012,7 +17012,7 @@
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>DIC_initial</t>
+          <t>dic_initial</t>
         </is>
       </c>
       <c r="L205" t="inlineStr">
@@ -17097,7 +17097,7 @@
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>DIC_slope</t>
+          <t>dic_slope</t>
         </is>
       </c>
       <c r="M206" t="n">
@@ -17177,7 +17177,7 @@
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>DIC_x50</t>
+          <t>dic_x50</t>
         </is>
       </c>
       <c r="M207" t="n">
@@ -17257,7 +17257,7 @@
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>DIC_min</t>
+          <t>dic_min</t>
         </is>
       </c>
       <c r="M208" t="n">
@@ -17337,7 +17337,7 @@
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>DIC_initial</t>
+          <t>dic_initial</t>
         </is>
       </c>
       <c r="L209" t="inlineStr">
@@ -17422,7 +17422,7 @@
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>DIC_slope</t>
+          <t>dic_slope</t>
         </is>
       </c>
       <c r="M210" t="n">
@@ -17502,7 +17502,7 @@
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>DIC_x50</t>
+          <t>dic_x50</t>
         </is>
       </c>
       <c r="M211" t="n">
@@ -17582,7 +17582,7 @@
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>DIC_min</t>
+          <t>dic_min</t>
         </is>
       </c>
       <c r="M212" t="n">
@@ -17662,7 +17662,7 @@
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>DIC_initial</t>
+          <t>dic_initial</t>
         </is>
       </c>
       <c r="L213" t="inlineStr">
@@ -17747,7 +17747,7 @@
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>DIC_slope</t>
+          <t>dic_slope</t>
         </is>
       </c>
       <c r="M214" t="n">
@@ -17827,7 +17827,7 @@
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>DIC_x50</t>
+          <t>dic_x50</t>
         </is>
       </c>
       <c r="M215" t="n">
@@ -17907,7 +17907,7 @@
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>DIC_min</t>
+          <t>dic_min</t>
         </is>
       </c>
       <c r="M216" t="n">
@@ -17987,7 +17987,7 @@
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>DIC_initial</t>
+          <t>dic_initial</t>
         </is>
       </c>
       <c r="L217" t="inlineStr">
@@ -18072,7 +18072,7 @@
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>DIC_slope</t>
+          <t>dic_slope</t>
         </is>
       </c>
       <c r="M218" t="n">
@@ -18152,7 +18152,7 @@
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>DIC_x50</t>
+          <t>dic_x50</t>
         </is>
       </c>
       <c r="M219" t="n">
@@ -18232,7 +18232,7 @@
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>DIC_min</t>
+          <t>dic_min</t>
         </is>
       </c>
       <c r="M220" t="n">
@@ -18312,7 +18312,7 @@
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>DIC_initial</t>
+          <t>dic_initial</t>
         </is>
       </c>
       <c r="L221" t="inlineStr">
@@ -18397,7 +18397,7 @@
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>DIC_slope</t>
+          <t>dic_slope</t>
         </is>
       </c>
       <c r="M222" t="n">
@@ -18477,7 +18477,7 @@
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>DIC_x50</t>
+          <t>dic_x50</t>
         </is>
       </c>
       <c r="M223" t="n">
@@ -18557,7 +18557,7 @@
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>DIC_min</t>
+          <t>dic_min</t>
         </is>
       </c>
       <c r="M224" t="n">
@@ -18637,7 +18637,7 @@
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>DIC_initial</t>
+          <t>dic_initial</t>
         </is>
       </c>
       <c r="L225" t="inlineStr">
@@ -18722,7 +18722,7 @@
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>DIC_slope</t>
+          <t>dic_slope</t>
         </is>
       </c>
       <c r="M226" t="n">
@@ -18802,7 +18802,7 @@
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>DIC_x50</t>
+          <t>dic_x50</t>
         </is>
       </c>
       <c r="M227" t="n">
@@ -18882,7 +18882,7 @@
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>DIC_min</t>
+          <t>dic_min</t>
         </is>
       </c>
       <c r="M228" t="n">
@@ -18962,7 +18962,7 @@
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>DIC_initial</t>
+          <t>dic_initial</t>
         </is>
       </c>
       <c r="L229" t="inlineStr">
@@ -19047,7 +19047,7 @@
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>DIC_slope</t>
+          <t>dic_slope</t>
         </is>
       </c>
       <c r="M230" t="n">
@@ -19127,7 +19127,7 @@
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>DIC_x50</t>
+          <t>dic_x50</t>
         </is>
       </c>
       <c r="M231" t="n">
@@ -19207,7 +19207,7 @@
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>DIC_min</t>
+          <t>dic_min</t>
         </is>
       </c>
       <c r="M232" t="n">
@@ -19287,7 +19287,7 @@
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>DIC_initial</t>
+          <t>dic_initial</t>
         </is>
       </c>
       <c r="L233" t="inlineStr">
@@ -19372,7 +19372,7 @@
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>DIC_slope</t>
+          <t>dic_slope</t>
         </is>
       </c>
       <c r="M234" t="n">
@@ -19452,7 +19452,7 @@
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>DIC_x50</t>
+          <t>dic_x50</t>
         </is>
       </c>
       <c r="M235" t="n">
@@ -19532,7 +19532,7 @@
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>DIC_min</t>
+          <t>dic_min</t>
         </is>
       </c>
       <c r="M236" t="n">
@@ -19612,7 +19612,7 @@
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>DIC_initial</t>
+          <t>dic_initial</t>
         </is>
       </c>
       <c r="L237" t="inlineStr">
@@ -19697,7 +19697,7 @@
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>DIC_slope</t>
+          <t>dic_slope</t>
         </is>
       </c>
       <c r="M238" t="n">
@@ -19777,7 +19777,7 @@
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>DIC_x50</t>
+          <t>dic_x50</t>
         </is>
       </c>
       <c r="M239" t="n">
@@ -19857,7 +19857,7 @@
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>DIC_min</t>
+          <t>dic_min</t>
         </is>
       </c>
       <c r="M240" t="n">
@@ -19937,7 +19937,7 @@
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>DIC_initial</t>
+          <t>dic_initial</t>
         </is>
       </c>
       <c r="L241" t="inlineStr">
@@ -20022,7 +20022,7 @@
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>DIC_slope</t>
+          <t>dic_slope</t>
         </is>
       </c>
       <c r="M242" t="n">
@@ -20102,7 +20102,7 @@
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>DIC_x50</t>
+          <t>dic_x50</t>
         </is>
       </c>
       <c r="M243" t="n">
@@ -20182,7 +20182,7 @@
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>DIC_min</t>
+          <t>dic_min</t>
         </is>
       </c>
       <c r="M244" t="n">
@@ -20262,7 +20262,7 @@
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>DIC_initial</t>
+          <t>dic_initial</t>
         </is>
       </c>
       <c r="L245" t="inlineStr">
@@ -20347,7 +20347,7 @@
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>DIC_slope</t>
+          <t>dic_slope</t>
         </is>
       </c>
       <c r="M246" t="n">
@@ -20427,7 +20427,7 @@
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>DIC_x50</t>
+          <t>dic_x50</t>
         </is>
       </c>
       <c r="M247" t="n">
@@ -20507,7 +20507,7 @@
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>DIC_min</t>
+          <t>dic_min</t>
         </is>
       </c>
       <c r="M248" t="n">
@@ -20587,7 +20587,7 @@
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>DIC_initial</t>
+          <t>dic_initial</t>
         </is>
       </c>
       <c r="L249" t="inlineStr">
@@ -20672,7 +20672,7 @@
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>DIC_slope</t>
+          <t>dic_slope</t>
         </is>
       </c>
       <c r="M250" t="n">
@@ -20752,7 +20752,7 @@
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>DIC_x50</t>
+          <t>dic_x50</t>
         </is>
       </c>
       <c r="M251" t="n">
@@ -20832,7 +20832,7 @@
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>DIC_min</t>
+          <t>dic_min</t>
         </is>
       </c>
       <c r="M252" t="n">
@@ -20912,7 +20912,7 @@
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>DIC_initial</t>
+          <t>dic_initial</t>
         </is>
       </c>
       <c r="L253" t="inlineStr">
@@ -20997,7 +20997,7 @@
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>DIC_slope</t>
+          <t>dic_slope</t>
         </is>
       </c>
       <c r="M254" t="n">
@@ -21077,7 +21077,7 @@
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>DIC_x50</t>
+          <t>dic_x50</t>
         </is>
       </c>
       <c r="M255" t="n">
@@ -21157,7 +21157,7 @@
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>DIC_min</t>
+          <t>dic_min</t>
         </is>
       </c>
       <c r="M256" t="n">
@@ -21237,7 +21237,7 @@
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>DIC_initial</t>
+          <t>dic_initial</t>
         </is>
       </c>
       <c r="L257" t="inlineStr">
@@ -21322,7 +21322,7 @@
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>DIC_slope</t>
+          <t>dic_slope</t>
         </is>
       </c>
       <c r="M258" t="n">
@@ -21402,7 +21402,7 @@
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>DIC_x50</t>
+          <t>dic_x50</t>
         </is>
       </c>
       <c r="M259" t="n">
@@ -21482,7 +21482,7 @@
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>DIC_min</t>
+          <t>dic_min</t>
         </is>
       </c>
       <c r="M260" t="n">
@@ -21562,7 +21562,7 @@
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>DIC_initial</t>
+          <t>dic_initial</t>
         </is>
       </c>
       <c r="L261" t="inlineStr">
@@ -21647,7 +21647,7 @@
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>DIC_slope</t>
+          <t>dic_slope</t>
         </is>
       </c>
       <c r="M262" t="n">
@@ -21727,7 +21727,7 @@
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t>DIC_x50</t>
+          <t>dic_x50</t>
         </is>
       </c>
       <c r="M263" t="n">
@@ -21807,7 +21807,7 @@
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t>DIC_min</t>
+          <t>dic_min</t>
         </is>
       </c>
       <c r="M264" t="n">
@@ -21887,7 +21887,7 @@
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t>DIC_initial</t>
+          <t>dic_initial</t>
         </is>
       </c>
       <c r="L265" t="inlineStr">
@@ -21972,7 +21972,7 @@
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t>DIC_slope</t>
+          <t>dic_slope</t>
         </is>
       </c>
       <c r="M266" t="n">
@@ -22052,7 +22052,7 @@
       </c>
       <c r="G267" t="inlineStr">
         <is>
-          <t>DIC_x50</t>
+          <t>dic_x50</t>
         </is>
       </c>
       <c r="M267" t="n">
@@ -22132,7 +22132,7 @@
       </c>
       <c r="G268" t="inlineStr">
         <is>
-          <t>DIC_min</t>
+          <t>dic_min</t>
         </is>
       </c>
       <c r="M268" t="n">
@@ -22212,7 +22212,7 @@
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t>DIC_initial</t>
+          <t>dic_initial</t>
         </is>
       </c>
       <c r="L269" t="inlineStr">
@@ -22297,7 +22297,7 @@
       </c>
       <c r="G270" t="inlineStr">
         <is>
-          <t>DIC_slope</t>
+          <t>dic_slope</t>
         </is>
       </c>
       <c r="M270" t="n">
@@ -22377,7 +22377,7 @@
       </c>
       <c r="G271" t="inlineStr">
         <is>
-          <t>DIC_x50</t>
+          <t>dic_x50</t>
         </is>
       </c>
       <c r="M271" t="n">
@@ -22457,7 +22457,7 @@
       </c>
       <c r="G272" t="inlineStr">
         <is>
-          <t>DIC_min</t>
+          <t>dic_min</t>
         </is>
       </c>
       <c r="M272" t="n">
@@ -22537,7 +22537,7 @@
       </c>
       <c r="G273" t="inlineStr">
         <is>
-          <t>DIC_initial</t>
+          <t>dic_initial</t>
         </is>
       </c>
       <c r="L273" t="inlineStr">
@@ -22622,7 +22622,7 @@
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t>DIC_slope</t>
+          <t>dic_slope</t>
         </is>
       </c>
       <c r="M274" t="n">
@@ -22702,7 +22702,7 @@
       </c>
       <c r="G275" t="inlineStr">
         <is>
-          <t>DIC_x50</t>
+          <t>dic_x50</t>
         </is>
       </c>
       <c r="M275" t="n">
@@ -22782,7 +22782,7 @@
       </c>
       <c r="G276" t="inlineStr">
         <is>
-          <t>DIC_min</t>
+          <t>dic_min</t>
         </is>
       </c>
       <c r="M276" t="n">
@@ -22862,7 +22862,7 @@
       </c>
       <c r="G277" t="inlineStr">
         <is>
-          <t>DIC_initial</t>
+          <t>dic_initial</t>
         </is>
       </c>
       <c r="L277" t="inlineStr">
@@ -22947,7 +22947,7 @@
       </c>
       <c r="G278" t="inlineStr">
         <is>
-          <t>DIC_slope</t>
+          <t>dic_slope</t>
         </is>
       </c>
       <c r="M278" t="n">
@@ -23027,7 +23027,7 @@
       </c>
       <c r="G279" t="inlineStr">
         <is>
-          <t>DIC_x50</t>
+          <t>dic_x50</t>
         </is>
       </c>
       <c r="M279" t="n">
@@ -23107,7 +23107,7 @@
       </c>
       <c r="G280" t="inlineStr">
         <is>
-          <t>DIC_min</t>
+          <t>dic_min</t>
         </is>
       </c>
       <c r="M280" t="n">
@@ -23187,7 +23187,7 @@
       </c>
       <c r="G281" t="inlineStr">
         <is>
-          <t>DIC_initial</t>
+          <t>dic_initial</t>
         </is>
       </c>
       <c r="L281" t="inlineStr">
@@ -23272,7 +23272,7 @@
       </c>
       <c r="G282" t="inlineStr">
         <is>
-          <t>DIC_slope</t>
+          <t>dic_slope</t>
         </is>
       </c>
       <c r="M282" t="n">
@@ -23352,7 +23352,7 @@
       </c>
       <c r="G283" t="inlineStr">
         <is>
-          <t>DIC_x50</t>
+          <t>dic_x50</t>
         </is>
       </c>
       <c r="M283" t="n">
@@ -23432,7 +23432,7 @@
       </c>
       <c r="G284" t="inlineStr">
         <is>
-          <t>DIC_min</t>
+          <t>dic_min</t>
         </is>
       </c>
       <c r="M284" t="n">
